--- a/data/trans_bre/IP16A05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 8,09</t>
+          <t>-16,51; 8,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 4,75</t>
+          <t>-27,69; 7,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 28,12</t>
+          <t>-10,43; 31,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 19,74</t>
+          <t>-7,45; 18,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 123,82</t>
+          <t>-100,0; 207,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,16; —</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 6,66</t>
+          <t>-33,06; 7,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 39,29</t>
+          <t>-1,62; 39,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,23; -3,64</t>
+          <t>-30,92; -3,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 7,41</t>
+          <t>-13,99; 6,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,23; 161,24</t>
+          <t>-97,14; 131,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-27,78; -3,15</t>
+          <t>-25,47; -3,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 34,76</t>
+          <t>-20,51; 33,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 57,11</t>
+          <t>7,64; 57,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 0,0</t>
+          <t>-21,72; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-77,83; 621,38</t>
+          <t>-80,86; 591,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 13,36</t>
+          <t>-12,76; 13,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 19,79</t>
+          <t>-4,87; 19,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 13,08</t>
+          <t>-8,52; 10,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 19,14</t>
+          <t>-8,14; 17,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 169,35</t>
+          <t>-63,95; 199,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 267,93</t>
+          <t>-29,5; 270,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,46; 384,84</t>
+          <t>-62,37; 318,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,98; 513,82</t>
+          <t>-73,01; 540,69</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 22,05</t>
+          <t>-2,1; 21,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 14,93</t>
+          <t>-15,4; 17,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 2,82</t>
+          <t>-32,03; 2,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 2,03</t>
+          <t>-9,52; 2,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-80,13; 316,16</t>
+          <t>-76,46; 324,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-90,17; 52,21</t>
+          <t>-89,49; 44,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 38,4</t>
+          <t>-15,91; 32,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 6,88</t>
+          <t>-31,96; 4,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 35,07</t>
+          <t>-5,67; 36,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 4,03</t>
+          <t>-7,43; 4,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 11,72</t>
+          <t>-2,3; 11,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 5,33</t>
+          <t>-8,51; 5,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 9,49</t>
+          <t>-2,22; 9,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 55,21</t>
+          <t>-56,16; 56,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 120,72</t>
+          <t>-14,91; 120,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-52,51; 58,16</t>
+          <t>-51,92; 61,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 283,89</t>
+          <t>-32,87; 245,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 8,7</t>
+          <t>-17,85; 7,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 7,6</t>
+          <t>-28,47; 4,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 31,23</t>
+          <t>-9,88; 29,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 18,61</t>
+          <t>-6,51; 20,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 207,92</t>
+          <t>-100,0; 197,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-80,16; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 7,04</t>
+          <t>-30,62; 6,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 39,93</t>
+          <t>-3,21; 39,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,92; -3,95</t>
+          <t>-34,06; -3,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 6,67</t>
+          <t>-14,73; 6,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-97,14; 131,06</t>
+          <t>-91,92; 74,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-25,47; -3,06</t>
+          <t>-27,84; -3,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,51; 33,32</t>
+          <t>-18,01; 36,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 57,66</t>
+          <t>8,0; 56,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 0,0</t>
+          <t>-22,41; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-80,86; 591,65</t>
+          <t>-78,71; 720,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 13,12</t>
+          <t>-12,2; 13,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 19,74</t>
+          <t>-4,47; 18,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 10,86</t>
+          <t>-8,12; 12,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 17,25</t>
+          <t>-6,66; 19,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,95; 199,42</t>
+          <t>-60,04; 191,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 270,38</t>
+          <t>-29,89; 259,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 318,77</t>
+          <t>-64,01; 333,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,01; 540,69</t>
+          <t>-68,78; 609,57</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 21,91</t>
+          <t>-2,35; 22,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 17,21</t>
+          <t>-15,92; 15,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-32,03; 2,62</t>
+          <t>-30,99; 1,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 2,54</t>
+          <t>-10,05; 2,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-76,46; 324,96</t>
+          <t>-79,61; 306,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-89,49; 44,62</t>
+          <t>-91,83; 39,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 32,34</t>
+          <t>-15,38; 33,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 4,43</t>
+          <t>-31,34; 8,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 36,19</t>
+          <t>-7,6; 33,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 4,44</t>
+          <t>-7,42; 4,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 11,65</t>
+          <t>-2,66; 11,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 5,43</t>
+          <t>-8,32; 5,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 9,14</t>
+          <t>-2,2; 9,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 56,39</t>
+          <t>-58,95; 52,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 120,54</t>
+          <t>-16,3; 120,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-51,92; 61,2</t>
+          <t>-49,95; 60,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-32,87; 245,97</t>
+          <t>-30,98; 259,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumieron medicamentos antibióticos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,29</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>103,84%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 7,45</t>
+          <t>-18,39; 8,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 4,76</t>
+          <t>-29,16; 4,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 29,74</t>
+          <t>-10,38; 28,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 20,04</t>
+          <t>-7,26; 18,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 197,9</t>
+          <t>-100,0; 123,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-7,88%</t>
+          <t>-10,65%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 6,27</t>
+          <t>-31,72; 6,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 39,47</t>
+          <t>0,91; 39,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,06; -3,86</t>
+          <t>-30,23; -3,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 6,57</t>
+          <t>-12,9; 6,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,92; 74,38</t>
+          <t>-91,23; 161,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-6,35</t>
+          <t>-6,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-27,84; -3,16</t>
+          <t>-27,78; -3,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 36,85</t>
+          <t>-19,08; 34,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 56,86</t>
+          <t>7,3; 57,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 0,0</t>
+          <t>-19,65; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-78,71; 720,17</t>
+          <t>-77,83; 621,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,46</t>
+          <t>6,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>103,58%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 13,11</t>
+          <t>-13,19; 13,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 18,46</t>
+          <t>-2,8; 19,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 12,9</t>
+          <t>-8,23; 13,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 19,49</t>
+          <t>-2,45; 17,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 191,89</t>
+          <t>-65,03; 169,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,89; 259,33</t>
+          <t>-24,03; 267,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,01; 333,51</t>
+          <t>-61,46; 384,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,78; 609,57</t>
+          <t>-40,9; 602,17</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-2,5</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-63,77%</t>
+          <t>-67,78%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 22,45</t>
+          <t>-2,41; 22,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 15,29</t>
+          <t>-17,13; 14,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,99; 1,94</t>
+          <t>-30,53; 2,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 2,35</t>
+          <t>-10,71; 1,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-79,61; 306,99</t>
+          <t>-80,13; 316,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-91,83; 39,16</t>
+          <t>-90,17; 52,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,49</t>
+          <t>11,09</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>239,31%</t>
+          <t>174,5%</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 33,43</t>
+          <t>-14,94; 38,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,34; 8,03</t>
+          <t>-32,72; 6,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 33,21</t>
+          <t>-10,21; 31,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>53,96%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 4,17</t>
+          <t>-7,59; 4,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 11,23</t>
+          <t>-2,11; 11,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 5,22</t>
+          <t>-8,39; 5,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 9,4</t>
+          <t>-1,35; 7,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 52,42</t>
+          <t>-54,82; 55,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 120,97</t>
+          <t>-14,18; 120,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-49,95; 60,51</t>
+          <t>-52,51; 58,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 259,49</t>
+          <t>-19,82; 236,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,175 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-5,01</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-10,27</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8,61</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-54,78%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-58,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.409514085779935</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.637507143726355</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.760005367927828</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.359017406617355</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.7012295895872273</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.6125127100957529</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.085465992732252</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.9649281519009268</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-18,39; 8,09</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-29,16; 4,75</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,38; 28,12</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-7,26; 18,54</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 123,82</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.759187911690304</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.761670652543646</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.597485588750788</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.938102823522721</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5619166111931269</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.172742992279672</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.961758829181114</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.443726034623291</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>2.323341101707282</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-11,71</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>21,88</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-14,78</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-53,78%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>315,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-10,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-31,72; 6,66</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,91; 39,29</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-30,23; -3,64</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-12,9; 6,93</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-91,23; 161,24</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.285190756208671</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6.209710294004623</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.499163748965454</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.1488305980337624</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.505228303152891</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>7.160480467942062</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1410693474478941</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-12,31</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,67</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28,07</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-6,04</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-7.717298565826329</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2.139671276493806</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-6.552924774066255</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-4.208018317400635</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-27,78; -3,15</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-19,08; 34,76</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7,3; 57,11</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-19,65; 0,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-77,83; 621,38</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.5901905011324</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>11.07204507296177</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-0.6313725817889205</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.556918303714533</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.048251908379323</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +795,187 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,06</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,24</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,79</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>103,58%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.72033814814499</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.842016787337984</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.014801484517869</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.594055289156899</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.3431699602362173</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-13,19; 13,36</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,8; 19,79</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-8,23; 13,08</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,45; 17,46</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-65,03; 169,35</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-24,03; 267,93</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-61,46; 384,84</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-40,9; 602,17</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.725584231856301</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.173284119513024</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.134957579410424</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.25822893591973</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.6858341061414177</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.289185872703142</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.25866450495419</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,06</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-13,42</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>280,12%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-2,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-58,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-67,78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,41; 22,05</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-17,13; 14,93</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-30,53; 2,82</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-10,71; 1,53</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-80,13; 316,16</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-90,17; 52,21</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.04320336086502292</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.381913404048125</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8736358551347723</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.559954250217485</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.015791348705732</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.418199239136225</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.5781300121879956</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.9661444074790555</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-8,03</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11,09</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-64,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>174,5%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.755067370380987</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.720989208991462</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.275212453417815</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.8801033864832796</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7060196453633706</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4086403279119559</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5991884168836062</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5043297460913216</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-14,94; 38,4</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-32,72; 6,88</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-10,21; 31,48</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.592917456435726</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.495665606360885</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.836809352715515</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.601089405138501</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.908259796844114</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.577546163665852</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>4.523855213859058</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>7.470814282010791</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +983,267 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-1,93</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4,78</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,97</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-17,76%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,31%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-11,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>53,96%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>1.261443899138736</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1079702792920526</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.251037410858544</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.5122286610903812</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>2.665981192052962</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.04177096175811285</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.5437430066361064</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.6395407894406965</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-7,59; 4,03</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 11,72</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-8,39; 5,33</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-1,35; 7,69</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-54,82; 55,21</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-14,18; 120,72</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-52,51; 58,16</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-19,82; 236,82</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.472095231401982</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.445359504587929</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.949808822048889</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.158410746573288</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="n">
+        <v>-0.8099860061723003</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.9175542815017882</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3.988194855263737</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.004581972825568</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.8701074700587045</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.4450137570412737</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="n">
+        <v>2.616400854920571</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.5846398481137686</v>
+      </c>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-0.4026018494475018</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-0.8590964647033106</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1.773110275560156</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="n">
+        <v>-0.2201756313169849</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.4819322033170773</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>1.349922894121495</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="n">
+        <v>-3.68409416990761</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-3.771204133680206</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-1.960676145917667</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="n">
+        <v>4.269980337366786</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1.861116957371272</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>5.882847896307783</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.6116481347177034</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.9906915002331891</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.02965947085295656</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.6241224672466121</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.2852001124837414</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.3665275039802758</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.01426674659725938</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.481143206226629</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.871646455422559</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.4666224835947596</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.315161956839676</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.4568431463727198</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.6679839662633289</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.147785771746349</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.4727441230510087</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.3081252450170748</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.578249571915308</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.738266089413459</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.162059460528885</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.734227056406346</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.4316092175888461</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1.440454260298574</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.8148922570932137</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>2.401138681979501</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1251,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
